--- a/templates/RTC_template.xlsx
+++ b/templates/RTC_template.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69261C57-D4A1-4242-8760-5F4251B657B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="1" xr2:uid="{DAA47E26-CFC5-4016-8B4F-812DF22F7E66}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="0" activeTab="0" xr2:uid="{DAA47E26-CFC5-4016-8B4F-812DF22F7E66}"/>
   </bookViews>
   <sheets>
     <sheet name="From" sheetId="1" r:id="rId2"/>
